--- a/tests/yuhi/settings.xlsx
+++ b/tests/yuhi/settings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\89625\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1221e7247ec036c5/PATMO/PATMO-yuhi/tests/yuhi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F53ECE4-7BF6-472F-9901-77554C2A8F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{4F53ECE4-7BF6-472F-9901-77554C2A8F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0A96EAA-F8B6-144E-B19A-381FF010FB3D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{06C37378-65EC-8349-A749-809AD85E710E}"/>
+    <workbookView xWindow="17720" yWindow="760" windowWidth="16840" windowHeight="21580" xr2:uid="{06C37378-65EC-8349-A749-809AD85E710E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -134,10 +134,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>32COS:6.8675359d7/1d5, 33COS:5.4499096d5/1d5, 34COS:3.0747112d6/1d5, 36COS:1.4743303d4/1d5, 32CS2:3.743042d7/1d5, 33CS2:2.970235d5/1d5, 34CS2:1.675657d6/1d5, 36CS2:8.034107d3/1d5, 32H2S:1.046224903d9/1d5, 33H2S:8.258314469d6/1d5, 34H2S:4.640087823d7/1d5, 36H2S:2.206299159d5/1d5, 32SO2:5.612610135d9/1d5, 33SO2:4.431101857d7/1d5, 34SO2:2.499182710d8/1d5, 36SO2:1.192576285d6/1d5, 32CH3SCH3:2.507371315d9/1d5, 33CH3SCH3:1.999471616d7/1d5, 34CH3SCH3:1.133146064d8/1d5, 36CH3SCH3:5.478112870d5/1d5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>constant_species</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -147,6 +143,10 @@
   </si>
   <si>
     <t xml:space="preserve">32COS:8.80d-3, 33COS:8.80d-3, 34COS:8.780036175d-3, 36COS:8.80d-3, 32SO2:7.15d-2, 33SO2:7.15d-2, 34SO2:7.15d-2, 36SO2:7.15d-2, 32CS2:3.0d-4, 33CS2:3.0d-4, 34CS2:3.0d-4, 36CS2:3.0d-4,  </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>32COS:5.4951739696d7/1d5, 33COS:4.3520906528d5/1d5, 34COS:2.4522905848d6/1d5, 36COS:0.8604213112d4/1d5, 32CS2:3.743714386d7/1d5, 33CS2:2.964810559d5/1d5, 34CS2:1.670514358d6/1d5, 36CS2:5.860727256d3/1d5, 32H2S:1.04643246d9/1d5, 33H2S:8.247250258d6/1d5, 34H2S:4.625934159d7/1d5, 36H2S:1.609483057d5/1d5, 32SO2:5.613738738d9/1d5, 33SO2:4.433466528d7/1d5, 34SO2:2.491566169d8/1d5, 36SO2:8.699801621d6/1d5, 32CH3SCH3:2.507302919d9/1d5, 33CH3SCH3:1.995407157d7/1d5, 34CH3SCH3:1.129434747d8/1d5, 36CH3SCH3:3.995351447d5/1d5</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -154,7 +154,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -239,7 +239,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -255,7 +255,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -572,14 +572,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8537C3E-DE4A-A54B-9562-BA16146EEF99}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
@@ -590,7 +590,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -601,7 +601,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>15</v>
       </c>
@@ -612,7 +612,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -623,7 +623,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -634,7 +634,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -645,7 +645,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="17" thickBot="1">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -656,7 +656,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="17" thickBot="1">
       <c r="A8" s="3" t="s">
         <v>22</v>
       </c>
@@ -667,7 +667,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>3</v>
       </c>
@@ -678,7 +678,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -689,7 +689,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -700,7 +700,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -711,7 +711,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13" s="1" t="s">
         <v>27</v>
       </c>
@@ -722,18 +722,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
       <c r="A15" s="1" t="s">
         <v>25</v>
       </c>
@@ -741,10 +741,10 @@
         <v>20</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
       <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
@@ -752,7 +752,7 @@
         <v>21</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
